--- a/BCRP data.xlsx
+++ b/BCRP data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Mesa de Inversiones\Bottom-Up\Franco\Semestral - Trabajos\Renzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B44B313-8760-4434-B790-A8827C486C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9C4A9F-E3E1-4BEF-A712-1AE0F61B1446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mensuales" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Reporte de Inflacion 2026" sheetId="4" r:id="rId3"/>
     <sheet name="Reporte de Inflacion 2017" sheetId="5" r:id="rId4"/>
     <sheet name="Reporte de Inflacion 2023" sheetId="6" r:id="rId5"/>
+    <sheet name="Proyeccion 2026-2027" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -43,7 +44,7 @@
     <definedName name="IQ_LTMMONTH" hidden="1">120000</definedName>
     <definedName name="IQ_MONTH">15000</definedName>
     <definedName name="IQ_MTD" hidden="1">800000</definedName>
-    <definedName name="IQ_NAMES_REVISION_DATE_" hidden="1">46210.6621180556</definedName>
+    <definedName name="IQ_NAMES_REVISION_DATE_" hidden="1">46210.1782407407</definedName>
     <definedName name="IQ_NTM">6000</definedName>
     <definedName name="IQ_QTD" hidden="1">750000</definedName>
     <definedName name="IQ_TODAY" hidden="1">0</definedName>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="449">
   <si>
     <t>PN01730AM</t>
   </si>
@@ -1371,6 +1372,51 @@
   </si>
   <si>
     <t>2016 I Trim.</t>
+  </si>
+  <si>
+    <t>BCRP</t>
+  </si>
+  <si>
+    <t>Larrain</t>
+  </si>
+  <si>
+    <t>Macrocapitales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoyo </t>
+  </si>
+  <si>
+    <t>Año Proyectado</t>
+  </si>
+  <si>
+    <t>Magnitud FEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Debil</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fuerte</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Extraordinario</t>
+  </si>
+  <si>
+    <t>Institucion</t>
+  </si>
+  <si>
+    <t>Coste del PBI</t>
+  </si>
+  <si>
+    <t>Fuente</t>
+  </si>
+  <si>
+    <t>RI Marzo 2026</t>
+  </si>
+  <si>
+    <t>RI Junio 2026</t>
+  </si>
+  <si>
+    <t>Meeting</t>
   </si>
 </sst>
 </file>
@@ -1390,12 +1436,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1410,9 +1462,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1428,6 +1482,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>209954</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>134833</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8B13A6E-F06F-C7E1-B25F-C504B26BA3B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6299200" y="196850"/>
+          <a:ext cx="4121554" cy="1042883"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>67869</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>146542</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>34918</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC06F1AA-4EC3-21F4-E699-24A5F6D93DC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6286500" y="1356919"/>
+          <a:ext cx="4070842" cy="1256099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1718,9 +1865,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G379"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1740,7 +1887,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -1760,7 +1907,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1783,7 +1930,7 @@
         <v>2.86071327496294</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1806,7 +1953,7 @@
         <v>3.2173815548851499</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1829,7 +1976,7 @@
         <v>4.9406035780983597</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1852,7 +1999,7 @@
         <v>2.8105775584777501</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1875,7 +2022,7 @@
         <v>-1.4445720510946201</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1898,7 +2045,7 @@
         <v>0.54925936154958399</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1921,7 +2068,7 @@
         <v>-0.837336678815499</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1944,7 +2091,7 @@
         <v>4.68934987152796</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1967,7 +2114,7 @@
         <v>4.4869724816397403</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1990,7 +2137,7 @@
         <v>4.5286276484206596</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2013,7 +2160,7 @@
         <v>7.0446292836199298</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2036,7 +2183,7 @@
         <v>2.5530412941913099</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2059,7 +2206,7 @@
         <v>2.5337472428862</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2082,7 +2229,7 @@
         <v>4.0015775042731097</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2105,7 +2252,7 @@
         <v>5.9602660231601803</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2128,7 +2275,7 @@
         <v>4.7818871623585597</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2151,7 +2298,7 @@
         <v>4.8018715617516401</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2174,7 +2321,7 @@
         <v>7.1673314891544599</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2197,7 +2344,7 @@
         <v>8.2595093329666298</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2220,7 +2367,7 @@
         <v>5.5197113202683097</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2243,7 +2390,7 @@
         <v>3.7259896662780498</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2266,7 +2413,7 @@
         <v>10.1559011607944</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2289,7 +2436,7 @@
         <v>3.61123459206854</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2312,7 +2459,7 @@
         <v>6.8643237741373904</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -2335,7 +2482,7 @@
         <v>6.0007024595465497</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2358,7 +2505,7 @@
         <v>11.2145768241525</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2381,7 +2528,7 @@
         <v>8.8758714667287695</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2404,7 +2551,7 @@
         <v>11.9636468484203</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2427,7 +2574,7 @@
         <v>10.421548778090401</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2450,7 +2597,7 @@
         <v>6.4180253219124497</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2473,7 +2620,7 @@
         <v>4.72658800998357</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2496,7 +2643,7 @@
         <v>7.7976702246265299</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -2519,7 +2666,7 @@
         <v>9.8820632098308199</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2542,7 +2689,7 @@
         <v>5.0654489226695603</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -2565,7 +2712,7 @@
         <v>9.5380541961484795</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -2588,7 +2735,7 @@
         <v>5.4496039078373899</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -2611,7 +2758,7 @@
         <v>6.0048329177970503</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -2634,7 +2781,7 @@
         <v>4.2372529898282103</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2657,7 +2804,7 @@
         <v>1.5267129211569299</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2680,7 +2827,7 @@
         <v>0.76979381612666598</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -2703,7 +2850,7 @@
         <v>-2.8373355737346699</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -2726,7 +2873,7 @@
         <v>0.51793649933999397</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2749,7 +2896,7 @@
         <v>5.7641745727438201</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -2772,7 +2919,7 @@
         <v>5.4865802294566004</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -2795,7 +2942,7 @@
         <v>3.8561965097084601</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -2818,7 +2965,7 @@
         <v>5.2319547560755897</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -2841,7 +2988,7 @@
         <v>4.08542945046191</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -2864,7 +3011,7 @@
         <v>8.6687655211643495</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -2887,7 +3034,7 @@
         <v>12.5144696491163</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -2910,7 +3057,7 @@
         <v>7.6763539444800299</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -2933,7 +3080,7 @@
         <v>10.097832079330299</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -2956,7 +3103,7 @@
         <v>9.7794926193689307</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -2979,7 +3126,7 @@
         <v>12.8025761857861</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -3002,7 +3149,7 @@
         <v>16.5204977692438</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -3025,7 +3172,7 @@
         <v>7.4884635667430297</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -3048,7 +3195,7 @@
         <v>8.3495335827403103</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -3071,7 +3218,7 @@
         <v>6.9724723469651702</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -3094,7 +3241,7 @@
         <v>7.8334425798299003</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -3117,7 +3264,7 @@
         <v>9.4868332692138502</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -3140,7 +3287,7 @@
         <v>5.7428109265632399</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -3163,7 +3310,7 @@
         <v>2.93357262613317</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -3186,7 +3333,7 @@
         <v>3.8816236849022001</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -3209,7 +3356,7 @@
         <v>-3.1394101433267299</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -3232,7 +3379,7 @@
         <v>1.89712088332908</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -3255,7 +3402,7 @@
         <v>1.9216080646679199</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -3278,7 +3425,7 @@
         <v>-3.2911926019164199</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -3301,7 +3448,7 @@
         <v>-0.49395280579388601</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -3324,7 +3471,7 @@
         <v>0.16187135088358601</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -3347,7 +3494,7 @@
         <v>3.9593615277700001</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -3370,7 +3517,7 @@
         <v>2.5078232560743201</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -3393,7 +3540,7 @@
         <v>0.72802889960851302</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -3416,7 +3563,7 @@
         <v>-6.5990371993974506E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -3439,7 +3586,7 @@
         <v>-2.6500998962821201</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -3462,7 +3609,7 @@
         <v>-6.8865432569532503</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -3485,7 +3632,7 @@
         <v>0.83217177204134896</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -3508,7 +3655,7 @@
         <v>-1.5699869459789899</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -3531,7 +3678,7 @@
         <v>2.5636369211424701</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -3554,7 +3701,7 @@
         <v>0.26622617353359102</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -3577,7 +3724,7 @@
         <v>18.0365056610311</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -3600,7 +3747,7 @@
         <v>17.909148952678201</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -3623,7 +3770,7 @@
         <v>19.018231956082399</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -3646,7 +3793,7 @@
         <v>21.238874755666199</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -3669,7 +3816,7 @@
         <v>17.569666202725902</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -3692,7 +3839,7 @@
         <v>30.496971923579199</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -3715,7 +3862,7 @@
         <v>26.719937206688702</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -3738,7 +3885,7 @@
         <v>20.398586491048999</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -3761,7 +3908,7 @@
         <v>25.0375387837232</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -3784,7 +3931,7 @@
         <v>19.7728135711527</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -3807,7 +3954,7 @@
         <v>15.197901175310101</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -3830,7 +3977,7 @@
         <v>22.114517197633301</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -3853,7 +4000,7 @@
         <v>-0.94940701114917003</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -3876,7 +4023,7 @@
         <v>6.2325015143128404</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -3899,7 +4046,7 @@
         <v>1.43987536168081</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -3922,7 +4069,7 @@
         <v>1.77034017671837</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -3945,7 +4092,7 @@
         <v>3.0740450403411801</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -3968,7 +4115,7 @@
         <v>-6.2489529971005604</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -3991,7 +4138,7 @@
         <v>1.1400341868889401</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -4014,7 +4161,7 @@
         <v>6.1817356410242903</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -4037,7 +4184,7 @@
         <v>-0.13171023799907</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -4060,7 +4207,7 @@
         <v>5.1322507987749901</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -4083,7 +4230,7 @@
         <v>8.3909127285332392</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -4106,7 +4253,7 @@
         <v>5.9748311658221001</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -4129,7 +4276,7 @@
         <v>9.1367781367580694</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -4152,7 +4299,7 @@
         <v>-0.54482182451130501</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -4175,7 +4322,7 @@
         <v>5.3851431531419998</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -4198,7 +4345,7 @@
         <v>3.09051870018977</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -4221,7 +4368,7 @@
         <v>2.8367899177704601</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -4244,7 +4391,7 @@
         <v>2.1652582434601402</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -4267,7 +4414,7 @@
         <v>4.7768283207175601</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -4290,7 +4437,7 @@
         <v>12.1112442903357</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -4313,7 +4460,7 @@
         <v>6.9707343001511601</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -4336,7 +4483,7 @@
         <v>8.42462373362285</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -4359,7 +4506,7 @@
         <v>3.11117553258023E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -4382,7 +4529,7 @@
         <v>0.49075501436506402</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -4405,7 +4552,7 @@
         <v>0.19599544870128599</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -4428,7 +4575,7 @@
         <v>7.7279038318896198</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -4451,7 +4598,7 @@
         <v>5.7443868670619898</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -4474,7 +4621,7 @@
         <v>5.0873797875890601</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -4497,7 +4644,7 @@
         <v>8.0142329865439503</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -4520,7 +4667,7 @@
         <v>12.9517618197597</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -4543,7 +4690,7 @@
         <v>7.7826238478142802</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -4566,7 +4713,7 @@
         <v>5.55489570198029</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -4589,7 +4736,7 @@
         <v>8.3782810881329208</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -4612,7 +4759,7 @@
         <v>4.4205432389019501</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -4635,7 +4782,7 @@
         <v>10.1054326864242</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -4658,7 +4805,7 @@
         <v>11.8249390054452</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -4681,7 +4828,7 @@
         <v>17.672872359381</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -4704,7 +4851,7 @@
         <v>9.1485674234806904</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -4727,7 +4874,7 @@
         <v>9.3957973262145202</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -4750,7 +4897,7 @@
         <v>15.342803152853101</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -4773,7 +4920,7 @@
         <v>12.1336802981868</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -4796,7 +4943,7 @@
         <v>11.410914284704401</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -4819,7 +4966,7 @@
         <v>5.3973097754515997</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -4842,7 +4989,7 @@
         <v>1.40427784568641</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -4865,7 +5012,7 @@
         <v>7.8582393963906698</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -4888,7 +5035,7 @@
         <v>7.6291208302815496</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -4911,7 +5058,7 @@
         <v>6.6047663613799701</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -4934,7 +5081,7 @@
         <v>3.7777747643234298</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -4957,7 +5104,7 @@
         <v>2.3861013189569702</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -4980,7 +5127,7 @@
         <v>0.97709787251297198</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -5003,7 +5150,7 @@
         <v>-0.699144110353904</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -5026,7 +5173,7 @@
         <v>-5.8093957733760702</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -5049,7 +5196,7 @@
         <v>-0.66074023719807196</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -5072,7 +5219,7 @@
         <v>-3.72549289781217</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>146</v>
       </c>
@@ -5095,7 +5242,7 @@
         <v>-4.5299742747484402</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>147</v>
       </c>
@@ -5118,7 +5265,7 @@
         <v>-2.9523848746236201</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>148</v>
       </c>
@@ -5141,7 +5288,7 @@
         <v>2.1232728078631302</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>149</v>
       </c>
@@ -5164,7 +5311,7 @@
         <v>-0.83354690513643803</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>150</v>
       </c>
@@ -5187,7 +5334,7 @@
         <v>3.1947218792388101</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>151</v>
       </c>
@@ -5210,7 +5357,7 @@
         <v>-0.32920972594662001</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>152</v>
       </c>
@@ -5233,7 +5380,7 @@
         <v>5.2999990377939703</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>153</v>
       </c>
@@ -5256,7 +5403,7 @@
         <v>8.1252913643878504</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>154</v>
       </c>
@@ -5279,7 +5426,7 @@
         <v>10.595785081008399</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>155</v>
       </c>
@@ -5302,7 +5449,7 @@
         <v>10.596034254425</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>156</v>
       </c>
@@ -5325,7 +5472,7 @@
         <v>3.7896272644268798</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>157</v>
       </c>
@@ -5348,7 +5495,7 @@
         <v>14.012633469217599</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>158</v>
       </c>
@@ -5371,7 +5518,7 @@
         <v>2.0138352382881402</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>159</v>
       </c>
@@ -5394,7 +5541,7 @@
         <v>18.183043821949902</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>160</v>
       </c>
@@ -5417,7 +5564,7 @@
         <v>3.3894675086936399</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>161</v>
       </c>
@@ -5440,7 +5587,7 @@
         <v>7.8968202621505599</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>162</v>
       </c>
@@ -5463,7 +5610,7 @@
         <v>7.3999819879488298</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>163</v>
       </c>
@@ -5486,7 +5633,7 @@
         <v>11.7558403898213</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>164</v>
       </c>
@@ -5509,7 +5656,7 @@
         <v>6.1857796489137797</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>165</v>
       </c>
@@ -5532,7 +5679,7 @@
         <v>6.6154570417994103</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>166</v>
       </c>
@@ -5555,7 +5702,7 @@
         <v>4.6362452217392001</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>167</v>
       </c>
@@ -5578,7 +5725,7 @@
         <v>3.40085041532287</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>168</v>
       </c>
@@ -5601,7 +5748,7 @@
         <v>13.235134049561101</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>169</v>
       </c>
@@ -5624,7 +5771,7 @@
         <v>2.7725131625379902</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>170</v>
       </c>
@@ -5647,7 +5794,7 @@
         <v>16.185069730679601</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>171</v>
       </c>
@@ -5670,7 +5817,7 @@
         <v>-3.3341652860534001</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>172</v>
       </c>
@@ -5693,7 +5840,7 @@
         <v>3.0386264268226402</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>173</v>
       </c>
@@ -5716,7 +5863,7 @@
         <v>1.8607365051779901</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>174</v>
       </c>
@@ -5739,7 +5886,7 @@
         <v>1.7772812684366499</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>175</v>
       </c>
@@ -5762,7 +5909,7 @@
         <v>-1.6184672860017999</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>176</v>
       </c>
@@ -5785,7 +5932,7 @@
         <v>-0.95580662338494604</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>177</v>
       </c>
@@ -5808,7 +5955,7 @@
         <v>2.1845987171816099</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>178</v>
       </c>
@@ -5831,7 +5978,7 @@
         <v>-0.57855295381246696</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>179</v>
       </c>
@@ -5854,7 +6001,7 @@
         <v>0.90334415493785203</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>180</v>
       </c>
@@ -5877,7 +6024,7 @@
         <v>-2.4554323390383699</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>181</v>
       </c>
@@ -5900,7 +6047,7 @@
         <v>-4.8092018665563199</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>182</v>
       </c>
@@ -5923,7 +6070,7 @@
         <v>-0.232317144798489</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>183</v>
       </c>
@@ -5946,7 +6093,7 @@
         <v>3.1964440883382199</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>184</v>
       </c>
@@ -5969,7 +6116,7 @@
         <v>-1.6113218341175</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>185</v>
       </c>
@@ -5992,7 +6139,7 @@
         <v>0.28222812222205501</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>186</v>
       </c>
@@ -6015,7 +6162,7 @@
         <v>-0.20152750194538199</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>187</v>
       </c>
@@ -6038,7 +6185,7 @@
         <v>9.6634033283755691</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>188</v>
       </c>
@@ -6061,7 +6208,7 @@
         <v>1.99400364536118</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>189</v>
       </c>
@@ -6084,7 +6231,7 @@
         <v>-4.5356945037393404</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>190</v>
       </c>
@@ -6107,7 +6254,7 @@
         <v>-2.0096752016212101</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>191</v>
       </c>
@@ -6130,7 +6277,7 @@
         <v>0.144288207287357</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>192</v>
       </c>
@@ -6153,7 +6300,7 @@
         <v>-2.2059441940608302</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>193</v>
       </c>
@@ -6176,7 +6323,7 @@
         <v>2.7922437951874199</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>194</v>
       </c>
@@ -6199,7 +6346,7 @@
         <v>5.05843408791588E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>195</v>
       </c>
@@ -6222,7 +6369,7 @@
         <v>-3.3550117102047001</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>196</v>
       </c>
@@ -6245,7 +6392,7 @@
         <v>3.00875895062851</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>197</v>
       </c>
@@ -6268,7 +6415,7 @@
         <v>-6.1628651334461102</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>198</v>
       </c>
@@ -6291,7 +6438,7 @@
         <v>0.56556146291279996</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>199</v>
       </c>
@@ -6314,7 +6461,7 @@
         <v>-6.03302919229459</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>200</v>
       </c>
@@ -6337,7 +6484,7 @@
         <v>-2.29185845556766</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>201</v>
       </c>
@@ -6360,7 +6507,7 @@
         <v>2.0321743552458198</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>202</v>
       </c>
@@ -6383,7 +6530,7 @@
         <v>3.1083692465027601</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>203</v>
       </c>
@@ -6406,7 +6553,7 @@
         <v>-1.83164718507721</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>204</v>
       </c>
@@ -6429,7 +6576,7 @@
         <v>0.47939750695342098</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>205</v>
       </c>
@@ -6452,7 +6599,7 @@
         <v>4.0118856186686997</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>206</v>
       </c>
@@ -6475,7 +6622,7 @@
         <v>-2.7442736692858301</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>207</v>
       </c>
@@ -6498,7 +6645,7 @@
         <v>3.1889069935825201</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>208</v>
       </c>
@@ -6521,7 +6668,7 @@
         <v>6.0253040702123997</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>209</v>
       </c>
@@ -6544,7 +6691,7 @@
         <v>5.4157083434056403</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>210</v>
       </c>
@@ -6567,7 +6714,7 @@
         <v>2.7176130427774901</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>211</v>
       </c>
@@ -6590,7 +6737,7 @@
         <v>3.8243960544679201</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>212</v>
       </c>
@@ -6613,7 +6760,7 @@
         <v>5.4495808380743096</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>213</v>
       </c>
@@ -6636,7 +6783,7 @@
         <v>2.1566516930064998</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>214</v>
       </c>
@@ -6659,7 +6806,7 @@
         <v>3.0102976387922502</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>215</v>
       </c>
@@ -6682,7 +6829,7 @@
         <v>-0.72428990417183903</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>216</v>
       </c>
@@ -6705,7 +6852,7 @@
         <v>-8.3780143791737899E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>217</v>
       </c>
@@ -6728,7 +6875,7 @@
         <v>-1.0327199727121601</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>218</v>
       </c>
@@ -6751,7 +6898,7 @@
         <v>-2.28211591028913</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>219</v>
       </c>
@@ -6774,7 +6921,7 @@
         <v>-5.8814597158839597E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>220</v>
       </c>
@@ -6797,7 +6944,7 @@
         <v>-1.5593473196008201</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>221</v>
       </c>
@@ -6820,7 +6967,7 @@
         <v>7.3991061094318704</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>222</v>
       </c>
@@ -6843,7 +6990,7 @@
         <v>4.65595179838202</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>223</v>
       </c>
@@ -6866,7 +7013,7 @@
         <v>9.0588011599255793</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>224</v>
       </c>
@@ -6889,7 +7036,7 @@
         <v>6.4190629689300396</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>225</v>
       </c>
@@ -6912,7 +7059,7 @@
         <v>10.106569715532</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>226</v>
       </c>
@@ -6935,7 +7082,7 @@
         <v>1.9065895032176099</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>227</v>
       </c>
@@ -6958,7 +7105,7 @@
         <v>6.7717161947267499</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>228</v>
       </c>
@@ -6981,7 +7128,7 @@
         <v>8.1795861618081194</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>229</v>
       </c>
@@ -7004,7 +7151,7 @@
         <v>7.3622084295373096</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>230</v>
       </c>
@@ -7027,7 +7174,7 @@
         <v>5.6666592628564896</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>231</v>
       </c>
@@ -7050,7 +7197,7 @@
         <v>7.5787912307242804</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>232</v>
       </c>
@@ -7073,7 +7220,7 @@
         <v>1.5692813927318301</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>233</v>
       </c>
@@ -7096,7 +7243,7 @@
         <v>-4.7806059536578402</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>234</v>
       </c>
@@ -7119,7 +7266,7 @@
         <v>-1.9984897860753701</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>235</v>
       </c>
@@ -7142,7 +7289,7 @@
         <v>-6.0595070113387104</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>236</v>
       </c>
@@ -7165,7 +7312,7 @@
         <v>-2.01410188490375</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>237</v>
       </c>
@@ -7188,7 +7335,7 @@
         <v>-3.9834163601308701</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>238</v>
       </c>
@@ -7211,7 +7358,7 @@
         <v>-3.06615972559577</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>239</v>
       </c>
@@ -7234,7 +7381,7 @@
         <v>3.7294097727428999</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>240</v>
       </c>
@@ -7257,7 +7404,7 @@
         <v>0.50514637987146804</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>241</v>
       </c>
@@ -7280,7 +7427,7 @@
         <v>-5.1454211707106703</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>242</v>
       </c>
@@ -7303,7 +7450,7 @@
         <v>5.9834748846179897</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>243</v>
       </c>
@@ -7326,7 +7473,7 @@
         <v>-1.8857359120669399</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>244</v>
       </c>
@@ -7349,7 +7496,7 @@
         <v>8.9003557262375299</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>245</v>
       </c>
@@ -7372,7 +7519,7 @@
         <v>9.4309213106579897</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>246</v>
       </c>
@@ -7395,7 +7542,7 @@
         <v>1.88466964711746</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>247</v>
       </c>
@@ -7418,7 +7565,7 @@
         <v>11.489655184268299</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>248</v>
       </c>
@@ -7441,7 +7588,7 @@
         <v>11.333931721978599</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>249</v>
       </c>
@@ -7464,7 +7611,7 @@
         <v>6.52573677967181</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>250</v>
       </c>
@@ -7487,7 +7634,7 @@
         <v>13.1099150396828</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>251</v>
       </c>
@@ -7510,7 +7657,7 @@
         <v>10.788053009725701</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>252</v>
       </c>
@@ -7533,7 +7680,7 @@
         <v>11.563790634809299</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>253</v>
       </c>
@@ -7556,7 +7703,7 @@
         <v>23.066331855243298</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>254</v>
       </c>
@@ -7579,7 +7726,7 @@
         <v>8.0397268955413708</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>255</v>
       </c>
@@ -7602,7 +7749,7 @@
         <v>23.589087374012902</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>256</v>
       </c>
@@ -7625,7 +7772,7 @@
         <v>16.148321527872898</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>257</v>
       </c>
@@ -7648,7 +7795,7 @@
         <v>22.672864746395401</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>258</v>
       </c>
@@ -7671,7 +7818,7 @@
         <v>33.019551875905798</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>259</v>
       </c>
@@ -7694,7 +7841,7 @@
         <v>15.851674493377899</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>260</v>
       </c>
@@ -7717,7 +7864,7 @@
         <v>14.1123326053855</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>261</v>
       </c>
@@ -7740,7 +7887,7 @@
         <v>19.352872567345699</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>262</v>
       </c>
@@ -7763,7 +7910,7 @@
         <v>14.4527065889431</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>263</v>
       </c>
@@ -7786,7 +7933,7 @@
         <v>15.6550403317222</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>264</v>
       </c>
@@ -7809,7 +7956,7 @@
         <v>11.635884640772099</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>265</v>
       </c>
@@ -7832,7 +7979,7 @@
         <v>5.4526429198019599</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>266</v>
       </c>
@@ -7855,7 +8002,7 @@
         <v>15.0540488538376</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>267</v>
       </c>
@@ -7878,7 +8025,7 @@
         <v>1.60379987468192</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>268</v>
       </c>
@@ -7901,7 +8048,7 @@
         <v>-2.5413808487755798</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>269</v>
       </c>
@@ -7924,7 +8071,7 @@
         <v>0.17579301581218401</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>270</v>
       </c>
@@ -7947,7 +8094,7 @@
         <v>-0.45667898289066</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>271</v>
       </c>
@@ -7970,7 +8117,7 @@
         <v>6.42469452789285</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>272</v>
       </c>
@@ -7993,7 +8140,7 @@
         <v>2.3380949634891302</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>273</v>
       </c>
@@ -8016,7 +8163,7 @@
         <v>3.86511650344098</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>274</v>
       </c>
@@ -8039,7 +8186,7 @@
         <v>7.4925665088746998</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>275</v>
       </c>
@@ -8062,7 +8209,7 @@
         <v>-1.1155682696217299</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>276</v>
       </c>
@@ -8085,7 +8232,7 @@
         <v>3.9838265652383602</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>277</v>
       </c>
@@ -8108,7 +8255,7 @@
         <v>6.0126376834804196</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>278</v>
       </c>
@@ -8131,7 +8278,7 @@
         <v>-1.69053785935635</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>279</v>
       </c>
@@ -8154,7 +8301,7 @@
         <v>-2.6137256869601901</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>280</v>
       </c>
@@ -8177,7 +8324,7 @@
         <v>4.8284161196444497</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>281</v>
       </c>
@@ -8200,7 +8347,7 @@
         <v>0.75491475414333298</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>282</v>
       </c>
@@ -8223,7 +8370,7 @@
         <v>1.9029318505955</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>283</v>
       </c>
@@ -8246,7 +8393,7 @@
         <v>-4.7663496024706902</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>284</v>
       </c>
@@ -8269,7 +8416,7 @@
         <v>-5.3661157853374801</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>285</v>
       </c>
@@ -8292,7 +8439,7 @@
         <v>-4.0994026209899799</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>286</v>
       </c>
@@ -8315,7 +8462,7 @@
         <v>0.56220523417768398</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>287</v>
       </c>
@@ -8338,7 +8485,7 @@
         <v>-2.5695941110575999</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>288</v>
       </c>
@@ -8361,7 +8508,7 @@
         <v>-2.8094975673251499</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>289</v>
       </c>
@@ -8384,7 +8531,7 @@
         <v>-1.3814731278510499</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>290</v>
       </c>
@@ -8407,7 +8554,7 @@
         <v>-1.28964885831507</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>291</v>
       </c>
@@ -8430,7 +8577,7 @@
         <v>-0.56054514155467805</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>292</v>
       </c>
@@ -8453,7 +8600,7 @@
         <v>0.36018571414284201</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>293</v>
       </c>
@@ -8476,7 +8623,7 @@
         <v>-2.5653330975417199</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>294</v>
       </c>
@@ -8499,7 +8646,7 @@
         <v>-1.33505633206434</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>295</v>
       </c>
@@ -8522,7 +8669,7 @@
         <v>-2.8970194744300102</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>296</v>
       </c>
@@ -8545,7 +8692,7 @@
         <v>0.26605805294894003</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>297</v>
       </c>
@@ -8568,7 +8715,7 @@
         <v>4.1608050650006696</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>298</v>
       </c>
@@ -8591,7 +8738,7 @@
         <v>-3.3575745626336602</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>299</v>
       </c>
@@ -8614,7 +8761,7 @@
         <v>0.69896514857383796</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>300</v>
       </c>
@@ -8637,7 +8784,7 @@
         <v>4.13437728767079</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>301</v>
       </c>
@@ -8660,7 +8807,7 @@
         <v>1.57560612380785</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>302</v>
       </c>
@@ -8683,7 +8830,7 @@
         <v>3.4048355436163602</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>303</v>
       </c>
@@ -8706,7 +8853,7 @@
         <v>3.0843415455443499</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>304</v>
       </c>
@@ -8729,7 +8876,7 @@
         <v>-21.981703563640501</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>305</v>
       </c>
@@ -8752,7 +8899,7 @@
         <v>-42.310680172362503</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>306</v>
       </c>
@@ -8775,7 +8922,7 @@
         <v>-45.780032542420301</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>307</v>
       </c>
@@ -8798,7 +8945,7 @@
         <v>-14.511300216711</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>308</v>
       </c>
@@ -8821,7 +8968,7 @@
         <v>-6.2672944514031403</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>309</v>
       </c>
@@ -8844,7 +8991,7 @@
         <v>-11.4626690436455</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>310</v>
       </c>
@@ -8867,7 +9014,7 @@
         <v>-12.550747021657299</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>311</v>
       </c>
@@ -8890,7 +9037,7 @@
         <v>-2.8710147334074501</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>312</v>
       </c>
@@ -8913,7 +9060,7 @@
         <v>-4.9019473251935697</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>313</v>
       </c>
@@ -8936,7 +9083,7 @@
         <v>-3.9328358859405101</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>314</v>
       </c>
@@ -8959,7 +9106,7 @@
         <v>-8.4530911051133604</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>315</v>
       </c>
@@ -8982,7 +9129,7 @@
         <v>-4.2885199898038104</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>316</v>
       </c>
@@ -9005,7 +9152,7 @@
         <v>15.591384931851501</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>317</v>
       </c>
@@ -9028,7 +9175,7 @@
         <v>58.0760397837592</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>318</v>
       </c>
@@ -9051,7 +9198,7 @@
         <v>67.045979973721799</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>319</v>
       </c>
@@ -9074,7 +9221,7 @@
         <v>7.8522876136505104</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>320</v>
       </c>
@@ -9097,7 +9244,7 @@
         <v>3.4028499331236799</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>321</v>
       </c>
@@ -9120,7 +9267,7 @@
         <v>5.4226177852699902</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>322</v>
       </c>
@@ -9143,7 +9290,7 @@
         <v>11.0372006691564</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>323</v>
       </c>
@@ -9166,7 +9313,7 @@
         <v>1.4968319082679</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>324</v>
       </c>
@@ -9189,7 +9336,7 @@
         <v>-5.2004806178188101</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>325</v>
       </c>
@@ -9212,7 +9359,7 @@
         <v>-5.4153620798763402</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>326</v>
       </c>
@@ -9235,7 +9382,7 @@
         <v>4.51891196263957</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>327</v>
       </c>
@@ -9258,7 +9405,7 @@
         <v>4.8109462301783999E-2</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>328</v>
       </c>
@@ -9281,7 +9428,7 @@
         <v>-0.77710845835095699</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>329</v>
       </c>
@@ -9304,7 +9451,7 @@
         <v>-0.62885830297425804</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>330</v>
       </c>
@@ -9327,7 +9474,7 @@
         <v>-5.8103931604549999</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>331</v>
       </c>
@@ -9350,7 +9497,7 @@
         <v>3.2272287931595098</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>332</v>
       </c>
@@ -9373,7 +9520,7 @@
         <v>-5.5793829145770601</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>333</v>
       </c>
@@ -9396,7 +9543,7 @@
         <v>-4.7920158474444099</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>334</v>
       </c>
@@ -9419,7 +9566,7 @@
         <v>-2.2232015612743998</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>335</v>
       </c>
@@ -9442,7 +9589,7 @@
         <v>2.4139210784873701</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>336</v>
       </c>
@@ -9465,7 +9612,7 @@
         <v>6.1999276046465299</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>337</v>
       </c>
@@ -9488,7 +9635,7 @@
         <v>9.4422738920970701</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>338</v>
       </c>
@@ -9511,7 +9658,7 @@
         <v>0.263679043450326</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>339</v>
       </c>
@@ -9534,7 +9681,7 @@
         <v>1.1714823444231099</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>340</v>
       </c>
@@ -9557,7 +9704,7 @@
         <v>10.2275011011053</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>341</v>
       </c>
@@ -9580,7 +9727,7 @@
         <v>18.229390630321401</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>342</v>
       </c>
@@ -9603,7 +9750,7 @@
         <v>18.261860342793501</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>343</v>
       </c>
@@ -9626,7 +9773,7 @@
         <v>17.249922273625199</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>344</v>
       </c>
@@ -9649,7 +9796,7 @@
         <v>12.449576039806001</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>345</v>
       </c>
@@ -9672,7 +9819,7 @@
         <v>8.2170613375507404</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>346</v>
       </c>
@@ -9695,7 +9842,7 @@
         <v>10.2571333645633</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>347</v>
       </c>
@@ -9718,7 +9865,7 @@
         <v>4.8874994681416197</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>348</v>
       </c>
@@ -9741,7 +9888,7 @@
         <v>8.9057153226945598</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>349</v>
       </c>
@@ -9764,7 +9911,7 @@
         <v>5.0427466754205597</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>350</v>
       </c>
@@ -9787,7 +9934,7 @@
         <v>6.25110723121725</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>351</v>
       </c>
@@ -9810,7 +9957,7 @@
         <v>18.534911017593899</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>352</v>
       </c>
@@ -9833,7 +9980,7 @@
         <v>4.1762533254065097</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>353</v>
       </c>
@@ -9856,7 +10003,7 @@
         <v>-2.9576201255019599</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>354</v>
       </c>
@@ -9879,7 +10026,7 @@
         <v>3.0474393541664102</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>355</v>
       </c>
@@ -9902,7 +10049,7 @@
         <v>-6.2676751621100797</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>356</v>
       </c>
@@ -9925,7 +10072,7 @@
         <v>4.2868688959121801</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>357</v>
       </c>
@@ -9948,7 +10095,7 @@
         <v>9.6874715439662005</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>358</v>
       </c>
@@ -9971,7 +10118,7 @@
         <v>2.2397621245888302</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>359</v>
       </c>
@@ -9994,7 +10141,7 @@
         <v>-0.98184617683689801</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>360</v>
       </c>
@@ -10017,7 +10164,7 @@
         <v>-0.91244754795294902</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>361</v>
       </c>
@@ -10040,7 +10187,7 @@
         <v>3.04580102334987</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>362</v>
       </c>
@@ -10063,7 +10210,7 @@
         <v>2.8120141608888698</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>363</v>
       </c>
@@ -10086,7 +10233,7 @@
         <v>-0.42433595971876498</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>364</v>
       </c>
@@ -10109,7 +10256,7 @@
         <v>7.8067602693773797</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>365</v>
       </c>
@@ -10132,7 +10279,7 @@
         <v>8.9402739751764706</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>366</v>
       </c>
@@ -10155,7 +10302,7 @@
         <v>-7.0561500027997903</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>367</v>
       </c>
@@ -10178,7 +10325,7 @@
         <v>1.01218002427487</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>368</v>
       </c>
@@ -10201,7 +10348,7 @@
         <v>2.2655637060026401</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>369</v>
       </c>
@@ -10224,7 +10371,7 @@
         <v>1.62261906785121</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>370</v>
       </c>
@@ -10247,7 +10394,7 @@
         <v>2.5761908104040101</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>371</v>
       </c>
@@ -10270,7 +10417,7 @@
         <v>7.3427523286571503</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>372</v>
       </c>
@@ -10293,7 +10440,7 @@
         <v>-5.8398997087288098</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>373</v>
       </c>
@@ -10316,7 +10463,7 @@
         <v>-1.61470901681864</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>374</v>
       </c>
@@ -10339,7 +10486,7 @@
         <v>3.3169637263913199</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>375</v>
       </c>
@@ -10362,7 +10509,7 @@
         <v>-1.11107795702728</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>376</v>
       </c>
@@ -10385,7 +10532,7 @@
         <v>-4.5593942012523501</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>377</v>
       </c>
@@ -10408,7 +10555,7 @@
         <v>-3.2369179635681902</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>378</v>
       </c>
@@ -10440,9 +10587,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G106"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="11.453125" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>389</v>
       </c>
@@ -10458,11 +10608,11 @@
       <c r="F1" t="s">
         <v>398</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>390</v>
       </c>
@@ -10478,11 +10628,11 @@
       <c r="F2" t="s">
         <v>397</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1922</v>
       </c>
@@ -10492,20 +10642,11 @@
       <c r="C3">
         <v>7.6213087658114604</v>
       </c>
-      <c r="D3">
-        <v>1.6042780748663099</v>
-      </c>
       <c r="E3">
         <v>6.8688448821417296</v>
       </c>
-      <c r="F3">
-        <v>1.63399671044108</v>
-      </c>
-      <c r="G3">
-        <v>9.2615348306329004</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1923</v>
       </c>
@@ -10515,20 +10656,11 @@
       <c r="C4">
         <v>12.574613277600999</v>
       </c>
-      <c r="D4">
-        <v>1.57894736842105</v>
-      </c>
       <c r="E4">
         <v>0.124041765480271</v>
       </c>
-      <c r="F4">
-        <v>5.4446740744838804</v>
-      </c>
-      <c r="G4">
-        <v>2.0111715205006999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1924</v>
       </c>
@@ -10538,20 +10670,11 @@
       <c r="C5">
         <v>19.424011851685201</v>
       </c>
-      <c r="D5">
-        <v>1.5544041450777299</v>
-      </c>
       <c r="E5">
         <v>4.0909177212185703</v>
       </c>
-      <c r="F5">
-        <v>5.6437393264022502</v>
-      </c>
-      <c r="G5">
-        <v>6.73329215199084</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1925</v>
       </c>
@@ -10561,20 +10684,11 @@
       <c r="C6">
         <v>10.7103460458908</v>
       </c>
-      <c r="D6">
-        <v>1.53061224489797</v>
-      </c>
       <c r="E6">
         <v>-2.65900566594844</v>
       </c>
-      <c r="F6">
-        <v>0.94220289258539902</v>
-      </c>
-      <c r="G6">
-        <v>-0.79814068752556</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1926</v>
       </c>
@@ -10584,20 +10698,11 @@
       <c r="C7">
         <v>18.638526618868301</v>
       </c>
-      <c r="D7">
-        <v>1.50753768844221</v>
-      </c>
       <c r="E7">
         <v>7.7063076948302003</v>
       </c>
-      <c r="F7">
-        <v>11.4809769039781</v>
-      </c>
-      <c r="G7">
-        <v>-1.6016190695225001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1927</v>
       </c>
@@ -10607,20 +10712,11 @@
       <c r="C8">
         <v>-2.7505962663861099</v>
       </c>
-      <c r="D8">
-        <v>1.73267326732672</v>
-      </c>
       <c r="E8">
         <v>2.6649384654530199</v>
       </c>
-      <c r="F8">
-        <v>3.5127612560741901</v>
-      </c>
-      <c r="G8">
-        <v>2.4068587942117898</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1928</v>
       </c>
@@ -10630,20 +10726,11 @@
       <c r="C9">
         <v>10.910353772062701</v>
       </c>
-      <c r="D9">
-        <v>1.4598540145985299</v>
-      </c>
       <c r="E9">
         <v>1.5008144857724399</v>
       </c>
-      <c r="F9">
-        <v>4.1551891793372997</v>
-      </c>
-      <c r="G9">
-        <v>-0.63824050818333</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1929</v>
       </c>
@@ -10653,20 +10740,11 @@
       <c r="C10">
         <v>16.9605324776449</v>
       </c>
-      <c r="D10">
-        <v>1.67865707434053</v>
-      </c>
       <c r="E10">
         <v>10.547998380506</v>
       </c>
-      <c r="F10">
-        <v>8.4315710785658702</v>
-      </c>
-      <c r="G10">
-        <v>4.3452877287546796</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1930</v>
       </c>
@@ -10677,19 +10755,13 @@
         <v>-8.4833422572651092</v>
       </c>
       <c r="D11">
-        <v>1.6509433962264199</v>
+        <v>1.6042780748663099</v>
       </c>
       <c r="E11">
         <v>-5.34694848443658</v>
       </c>
-      <c r="F11">
-        <v>3.62667652589808</v>
-      </c>
-      <c r="G11">
-        <v>4.3730583076632099</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1931</v>
       </c>
@@ -10700,19 +10772,13 @@
         <v>-20.039401572438599</v>
       </c>
       <c r="D12">
-        <v>1.6241299303944201</v>
+        <v>1.57894736842105</v>
       </c>
       <c r="E12">
         <v>-5.3699681479752899</v>
       </c>
-      <c r="F12">
-        <v>4.5290965187586396</v>
-      </c>
-      <c r="G12">
-        <v>5.1231007558047299</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1932</v>
       </c>
@@ -10723,19 +10789,13 @@
         <v>-15.574139365625101</v>
       </c>
       <c r="D13">
-        <v>32.191780821917803</v>
+        <v>1.5544041450777299</v>
       </c>
       <c r="E13">
         <v>3.6306767525824202</v>
       </c>
-      <c r="F13">
-        <v>7.3522616789174302</v>
-      </c>
-      <c r="G13">
-        <v>5.8777437978957998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1933</v>
       </c>
@@ -10746,19 +10806,13 @@
         <v>28.4207741010174</v>
       </c>
       <c r="D14">
-        <v>85.492227979274602</v>
+        <v>1.53061224489797</v>
       </c>
       <c r="E14">
         <v>7.1690499773227998</v>
       </c>
-      <c r="F14">
-        <v>3.1806295432933598</v>
-      </c>
-      <c r="G14">
-        <v>9.2122811137238294</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1934</v>
       </c>
@@ -10769,19 +10823,13 @@
         <v>22.5170882617304</v>
       </c>
       <c r="D15">
-        <v>77.374301675977605</v>
+        <v>1.50753768844221</v>
       </c>
       <c r="E15">
         <v>8.5561324800923</v>
       </c>
-      <c r="F15">
-        <v>2.89263898066827</v>
-      </c>
-      <c r="G15">
-        <v>10.576338394414</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1935</v>
       </c>
@@ -10792,19 +10840,13 @@
         <v>11.734554601203101</v>
       </c>
       <c r="D16">
-        <v>26.876640419947499</v>
+        <v>1.73267326732672</v>
       </c>
       <c r="E16">
         <v>7.4576454895570903</v>
       </c>
-      <c r="F16">
-        <v>7.5840571152043603</v>
-      </c>
-      <c r="G16">
-        <v>9.65160189410099</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1936</v>
       </c>
@@ -10815,19 +10857,13 @@
         <v>7.9467049423138603</v>
       </c>
       <c r="D17">
-        <v>13.2395531650807</v>
+        <v>1.4598540145985299</v>
       </c>
       <c r="E17">
         <v>1.7872830564395199</v>
       </c>
-      <c r="F17">
-        <v>-0.61353544092411005</v>
-      </c>
-      <c r="G17">
-        <v>1.6666775963530001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1937</v>
       </c>
@@ -10838,19 +10874,13 @@
         <v>0.24774733813066499</v>
       </c>
       <c r="D18">
-        <v>181.80489587139201</v>
+        <v>1.67865707434053</v>
       </c>
       <c r="E18">
         <v>-2.7121672724250598</v>
       </c>
-      <c r="F18">
-        <v>-0.32264615369515998</v>
-      </c>
-      <c r="G18">
-        <v>11.1580719271177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1938</v>
       </c>
@@ -10861,19 +10891,13 @@
         <v>5.0999324712506698E-2</v>
       </c>
       <c r="D19">
-        <v>-5.0304680409697902</v>
+        <v>1.6509433962264199</v>
       </c>
       <c r="E19">
         <v>2.1661165809365501</v>
       </c>
-      <c r="F19">
-        <v>4.5040233076495904</v>
-      </c>
-      <c r="G19">
-        <v>6.8609237965196099</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1939</v>
       </c>
@@ -10884,19 +10908,13 @@
         <v>-10.666924555444099</v>
       </c>
       <c r="D20">
-        <v>7.8361774744027297</v>
+        <v>1.6241299303944201</v>
       </c>
       <c r="E20">
         <v>2.6030829198009799</v>
       </c>
-      <c r="F20">
-        <v>4.2476698672302602</v>
-      </c>
-      <c r="G20">
-        <v>6.6814057136362903</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1940</v>
       </c>
@@ -10907,19 +10925,13 @@
         <v>-1.9648439085779199</v>
       </c>
       <c r="D21">
-        <v>10.0898847955437</v>
+        <v>32.191780821917803</v>
       </c>
       <c r="E21">
         <v>4.4362181968636598</v>
       </c>
-      <c r="F21">
-        <v>5.42174683261561</v>
-      </c>
-      <c r="G21">
-        <v>5.9730313339573202</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1941</v>
       </c>
@@ -10930,19 +10942,13 @@
         <v>-5.2935249216668696</v>
       </c>
       <c r="D22">
-        <v>36.6835326586937</v>
+        <v>85.492227979274602</v>
       </c>
       <c r="E22">
         <v>-4.3115557076227899</v>
       </c>
-      <c r="F22">
-        <v>-2.5229046017499099</v>
-      </c>
-      <c r="G22">
-        <v>3.7472649061890499</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1942</v>
       </c>
@@ -10953,19 +10959,13 @@
         <v>6.4864746691540898</v>
       </c>
       <c r="D23">
-        <v>25.7025071512704</v>
+        <v>77.374301675977605</v>
       </c>
       <c r="E23">
         <v>-4.7103307346924099</v>
       </c>
-      <c r="F23">
-        <v>6.6155158807324597</v>
-      </c>
-      <c r="G23">
-        <v>2.3727967631526901</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1943</v>
       </c>
@@ -10976,19 +10976,13 @@
         <v>3.9548331907613301</v>
       </c>
       <c r="D24">
-        <v>4.4444444444444402</v>
+        <v>26.876640419947499</v>
       </c>
       <c r="E24">
         <v>-6.5532598427270301</v>
       </c>
-      <c r="F24">
-        <v>9.4597028975817796</v>
-      </c>
-      <c r="G24">
-        <v>2.45380432681814</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1944</v>
       </c>
@@ -10999,19 +10993,13 @@
         <v>-0.100063197809135</v>
       </c>
       <c r="D25">
-        <v>8.5106382978723403</v>
+        <v>13.2395531650807</v>
       </c>
       <c r="E25">
         <v>8.4455818016583493</v>
       </c>
-      <c r="F25">
-        <v>3.0592485165454</v>
-      </c>
-      <c r="G25">
-        <v>2.3616051901795498</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1945</v>
       </c>
@@ -11022,19 +11010,13 @@
         <v>-3.6955031894142998</v>
       </c>
       <c r="D26">
-        <v>-13.7254901960784</v>
+        <v>181.80489587139201</v>
       </c>
       <c r="E26">
         <v>4.0557637058438596</v>
       </c>
-      <c r="F26">
-        <v>3.6617771156346501</v>
-      </c>
-      <c r="G26">
-        <v>4.0594482916463903</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1946</v>
       </c>
@@ -11045,19 +11027,13 @@
         <v>-11.709455514196</v>
       </c>
       <c r="D27">
-        <v>31.818181818181799</v>
+        <v>-5.0304680409697902</v>
       </c>
       <c r="E27">
         <v>2.3253745040688898</v>
       </c>
-      <c r="F27">
-        <v>-0.92263513740425696</v>
-      </c>
-      <c r="G27">
-        <v>3.16369862469034</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1947</v>
       </c>
@@ -11068,19 +11044,13 @@
         <v>0.991748774199536</v>
       </c>
       <c r="D28">
-        <v>17.241379310344801</v>
+        <v>7.8361774744027297</v>
       </c>
       <c r="E28">
         <v>-0.57030595793556005</v>
       </c>
-      <c r="F28">
-        <v>-7.5915623037303801</v>
-      </c>
-      <c r="G28">
-        <v>-11.869828663848701</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1948</v>
       </c>
@@ -11091,19 +11061,13 @@
         <v>2.54928593902279</v>
       </c>
       <c r="D29">
-        <v>25</v>
+        <v>10.0898847955437</v>
       </c>
       <c r="E29">
         <v>3.7956721697751199</v>
       </c>
-      <c r="F29">
-        <v>6.3893139547329696</v>
-      </c>
-      <c r="G29">
-        <v>15.4816563888501</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1949</v>
       </c>
@@ -11114,19 +11078,13 @@
         <v>11.7281410030955</v>
       </c>
       <c r="D30">
-        <v>11.764705882352899</v>
+        <v>36.6835326586937</v>
       </c>
       <c r="E30">
         <v>6.8533601727417404</v>
       </c>
-      <c r="F30">
-        <v>0.90881374412055005</v>
-      </c>
-      <c r="G30">
-        <v>3.3351046339961399</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1950</v>
       </c>
@@ -11137,19 +11095,13 @@
         <v>8.1720497324281105</v>
       </c>
       <c r="D31">
-        <v>49.473684210526301</v>
+        <v>25.7025071512704</v>
       </c>
       <c r="E31">
         <v>3.6674190996254499</v>
       </c>
-      <c r="F31">
-        <v>3.7374032599298301</v>
-      </c>
-      <c r="G31">
-        <v>-1.4314365974834</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1951</v>
       </c>
@@ -11160,19 +11112,13 @@
         <v>7.8909952606635096</v>
       </c>
       <c r="D32">
-        <v>61.267605633802802</v>
+        <v>4.4444444444444402</v>
       </c>
       <c r="E32">
         <v>3.0093624609897498</v>
       </c>
-      <c r="F32">
-        <v>4.8360981798516596</v>
-      </c>
-      <c r="G32">
-        <v>3.14778980342005</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1952</v>
       </c>
@@ -11183,19 +11129,13 @@
         <v>3.3164946189325701</v>
       </c>
       <c r="D33">
-        <v>36.244541484716201</v>
+        <v>8.5106382978723403</v>
       </c>
       <c r="E33">
         <v>2.8998052369616998</v>
       </c>
-      <c r="F33">
-        <v>3.15216443165242</v>
-      </c>
-      <c r="G33">
-        <v>3.52700228627072</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1953</v>
       </c>
@@ -11206,13 +11146,13 @@
         <v>-5.8035714285714297</v>
       </c>
       <c r="D34">
-        <v>41.025641025641001</v>
+        <v>-13.7254901960784</v>
       </c>
       <c r="E34">
         <v>2.3133543638275502</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1954</v>
       </c>
@@ -11223,13 +11163,13 @@
         <v>33.604152561498502</v>
       </c>
       <c r="D35">
-        <v>28.863636363636399</v>
+        <v>31.818181818181799</v>
       </c>
       <c r="E35">
         <v>1.9938335046248701</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1955</v>
       </c>
@@ -11240,13 +11180,13 @@
         <v>0.69256756756756799</v>
       </c>
       <c r="D36">
-        <v>4.2328042328042299</v>
+        <v>17.241379310344801</v>
       </c>
       <c r="E36">
         <v>-0.80612656187021403</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1956</v>
       </c>
@@ -11257,13 +11197,13 @@
         <v>10.6022479449757</v>
       </c>
       <c r="D37">
-        <v>28.934010152284301</v>
+        <v>25</v>
       </c>
       <c r="E37">
         <v>-4.7947988622511204</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1957</v>
       </c>
@@ -11274,13 +11214,13 @@
         <v>9.6010920673441493</v>
       </c>
       <c r="D38">
-        <v>-17.3228346456693</v>
+        <v>11.764705882352899</v>
       </c>
       <c r="E38">
         <v>0.40546308151942001</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1958</v>
       </c>
@@ -11291,13 +11231,13 @@
         <v>-9.4104622197619694</v>
       </c>
       <c r="D39">
-        <v>18.095238095238098</v>
+        <v>49.473684210526301</v>
       </c>
       <c r="E39">
         <v>6.9075451647183801</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1959</v>
       </c>
@@ -11308,13 +11248,13 @@
         <v>2.1998166819431701</v>
       </c>
       <c r="D40">
-        <v>14.1129032258065</v>
+        <v>61.267605633802802</v>
       </c>
       <c r="E40">
         <v>4.8906560636182901</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1960</v>
       </c>
@@ -11325,13 +11265,13 @@
         <v>49.506726457399097</v>
       </c>
       <c r="D41">
-        <v>1.7667844522968199</v>
+        <v>36.244541484716201</v>
       </c>
       <c r="E41">
         <v>6.40636846095527</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1961</v>
       </c>
@@ -11342,13 +11282,13 @@
         <v>9.2981403719256104</v>
       </c>
       <c r="D42">
-        <v>-10.185185185185199</v>
+        <v>41.025641025641001</v>
       </c>
       <c r="E42">
         <v>2.9925187032418998</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1962</v>
       </c>
@@ -11359,13 +11299,13 @@
         <v>-4.9030369557263098</v>
       </c>
       <c r="D43">
-        <v>32.860824742268001</v>
+        <v>28.863636363636399</v>
       </c>
       <c r="E43">
         <v>2.4040124524386002</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1963</v>
       </c>
@@ -11376,13 +11316,13 @@
         <v>6.4063101192766503</v>
       </c>
       <c r="D44">
-        <v>-31.037827352085401</v>
+        <v>4.2328042328042299</v>
       </c>
       <c r="E44">
         <v>1.5031244722175301</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1964</v>
       </c>
@@ -11393,13 +11333,13 @@
         <v>4.9990960043391803</v>
       </c>
       <c r="D45">
-        <v>-46.835443037974699</v>
+        <v>28.934010152284301</v>
       </c>
       <c r="E45">
         <v>4.9084858569051599</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1965</v>
       </c>
@@ -11410,13 +11350,13 @@
         <v>1.49806284976324</v>
       </c>
       <c r="D46">
-        <v>-27.513227513227498</v>
+        <v>-17.3228346456693</v>
       </c>
       <c r="E46">
         <v>1.99841395717684</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1966</v>
       </c>
@@ -11427,13 +11367,13 @@
         <v>9.7972686402578706</v>
       </c>
       <c r="D47">
-        <v>39.781021897810199</v>
+        <v>18.095238095238098</v>
       </c>
       <c r="E47">
         <v>5.3957393873425596</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1967</v>
       </c>
@@ -11444,13 +11384,13 @@
         <v>1.20519159456119</v>
       </c>
       <c r="D48">
-        <v>-11.2271540469974</v>
+        <v>14.1129032258065</v>
       </c>
       <c r="E48">
         <v>3.8949542637946299</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1968</v>
       </c>
@@ -11461,13 +11401,13 @@
         <v>6.19847328244275</v>
       </c>
       <c r="D49">
-        <v>17.647058823529399</v>
+        <v>1.7667844522968199</v>
       </c>
       <c r="E49">
         <v>-3.3939221811985201</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1969</v>
       </c>
@@ -11478,13 +11418,13 @@
         <v>-0.69723979298447403</v>
       </c>
       <c r="D50">
-        <v>-12.75</v>
+        <v>-10.185185185185199</v>
       </c>
       <c r="E50">
         <v>6.6000293987946499</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1970</v>
       </c>
@@ -11495,13 +11435,13 @@
         <v>7.1009771986970698</v>
       </c>
       <c r="D51">
-        <v>26.3610315186246</v>
+        <v>32.860824742268001</v>
       </c>
       <c r="E51">
         <v>7.8047435190292296</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1971</v>
       </c>
@@ -11512,13 +11452,13 @@
         <v>-6.0759664774263298</v>
       </c>
       <c r="D52">
-        <v>12.0181405895692</v>
+        <v>-31.037827352085401</v>
       </c>
       <c r="E52">
         <v>2.0081862368892298</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1972</v>
       </c>
@@ -11529,13 +11469,13 @@
         <v>6.2603439591278702</v>
       </c>
       <c r="D53">
-        <v>-16.599190283400802</v>
+        <v>-46.835443037974699</v>
       </c>
       <c r="E53">
         <v>-2.3949843260188102</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1973</v>
       </c>
@@ -11546,13 +11486,13 @@
         <v>3.7854675966682501</v>
       </c>
       <c r="D54">
-        <v>9.2233009708737903</v>
+        <v>-27.513227513227498</v>
       </c>
       <c r="E54">
         <v>0.39825282631038</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>1974</v>
       </c>
@@ -11563,13 +11503,13 @@
         <v>5.5657053373352499</v>
       </c>
       <c r="D55">
-        <v>17.3333333333333</v>
+        <v>39.781021897810199</v>
       </c>
       <c r="E55">
         <v>3.6980166346768999</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>1975</v>
       </c>
@@ -11580,13 +11520,13 @@
         <v>-7.7569689103158401</v>
       </c>
       <c r="D56">
-        <v>-29.734848484848499</v>
+        <v>-11.2271540469974</v>
       </c>
       <c r="E56">
         <v>-3.7018756169792701E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>1976</v>
       </c>
@@ -11597,13 +11537,13 @@
         <v>5.9769498793888998</v>
       </c>
       <c r="D57">
-        <v>46.361185983827497</v>
+        <v>17.647058823529399</v>
       </c>
       <c r="E57">
         <v>1.49364276015307</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>1977</v>
       </c>
@@ -11614,13 +11554,13 @@
         <v>20.864946889226101</v>
       </c>
       <c r="D58">
-        <v>17.1270718232044</v>
+        <v>-12.75</v>
       </c>
       <c r="E58">
         <v>-9.7299927025054703E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>1978</v>
       </c>
@@ -11631,13 +11571,13 @@
         <v>31.308851224105499</v>
       </c>
       <c r="D59">
-        <v>32.075471698113198</v>
+        <v>26.3610315186246</v>
       </c>
       <c r="E59">
         <v>-1.4974433893352801</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>1979</v>
       </c>
@@ -11648,13 +11588,13 @@
         <v>17.740329070554999</v>
       </c>
       <c r="D60">
-        <v>-11.9047619047619</v>
+        <v>12.0181405895692</v>
       </c>
       <c r="E60">
         <v>3.8932146829810899</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>1980</v>
       </c>
@@ -11665,13 +11605,13 @@
         <v>2.0877038641131498</v>
       </c>
       <c r="D61">
-        <v>18.3783783783784</v>
+        <v>-16.599190283400802</v>
       </c>
       <c r="E61">
         <v>-5.81727337615989</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>1981</v>
       </c>
@@ -11682,13 +11622,13 @@
         <v>-3.07580126611647</v>
       </c>
       <c r="D62">
-        <v>5.2511415525114096</v>
+        <v>9.2233009708737903</v>
       </c>
       <c r="E62">
         <v>9.0438297334849107</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>1982</v>
       </c>
@@ -11699,13 +11639,13 @@
         <v>1.23106384433882</v>
       </c>
       <c r="D63">
-        <v>-0.65075921908893697</v>
+        <v>17.3333333333333</v>
       </c>
       <c r="E63">
         <v>2.2124406347735399</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>1983</v>
       </c>
@@ -11716,13 +11656,13 @@
         <v>-9.8131946086545305</v>
       </c>
       <c r="D64">
-        <v>-10.698689956331901</v>
+        <v>-29.734848484848499</v>
       </c>
       <c r="E64">
         <v>-9.6328195829555803</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>1984</v>
       </c>
@@ -11733,13 +11673,13 @@
         <v>4.7756386246160796</v>
       </c>
       <c r="D65">
-        <v>12.8361858190709</v>
+        <v>46.361185983827497</v>
       </c>
       <c r="E65">
         <v>10.233258088788601</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>1985</v>
       </c>
@@ -11750,13 +11690,13 @@
         <v>4.2970006792264002</v>
       </c>
       <c r="D66">
-        <v>21.018418201516798</v>
+        <v>17.1270718232044</v>
       </c>
       <c r="E66">
         <v>2.9124004550625702</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>1986</v>
       </c>
@@ -11767,13 +11707,13 @@
         <v>-4.47986289631534</v>
       </c>
       <c r="D67">
-        <v>28.908387069180701</v>
+        <v>32.075471698113198</v>
       </c>
       <c r="E67">
         <v>4.33340703073182</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>1987</v>
       </c>
@@ -11784,13 +11724,13 @@
         <v>-2.9855030859767502</v>
       </c>
       <c r="D68">
-        <v>-15.0920254264989</v>
+        <v>-11.9047619047619</v>
       </c>
       <c r="E68">
         <v>6.59037931765205</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>1988</v>
       </c>
@@ -11801,13 +11741,13 @@
         <v>-14.9874241751738</v>
       </c>
       <c r="D69">
-        <v>-2.2165468599247</v>
+        <v>18.3783783783784</v>
       </c>
       <c r="E69">
         <v>7.0775347912524804</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>1989</v>
       </c>
@@ -11818,13 +11758,13 @@
         <v>-4.8686042464322998</v>
       </c>
       <c r="D70">
-        <v>-0.48686488697555302</v>
+        <v>5.2511415525114096</v>
       </c>
       <c r="E70">
         <v>-5.5978462681024901</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>1990</v>
       </c>
@@ -11835,13 +11775,13 @@
         <v>-8.6896867139263705</v>
       </c>
       <c r="D71">
-        <v>-9.3948408194301596</v>
+        <v>-0.65075921908893697</v>
       </c>
       <c r="E71">
         <v>-6.9426688956632896</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>1991</v>
       </c>
@@ -11852,13 +11792,13 @@
         <v>2.1287252692211398</v>
       </c>
       <c r="D72">
-        <v>32.594630974299697</v>
+        <v>-10.698689956331901</v>
       </c>
       <c r="E72">
         <v>3.1596745218218301</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>1992</v>
       </c>
@@ -11869,13 +11809,13 @@
         <v>-2.5993133889161402</v>
       </c>
       <c r="D73">
-        <v>19.618331519747599</v>
+        <v>12.8361858190709</v>
       </c>
       <c r="E73">
         <v>-7.7033394796148302</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>1993</v>
       </c>
@@ -11886,13 +11826,13 @@
         <v>8.1470292044310195</v>
       </c>
       <c r="D74">
-        <v>-13.0499616031404</v>
+        <v>21.018418201516798</v>
       </c>
       <c r="E74">
         <v>9.2674805771365207</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>1994</v>
       </c>
@@ -11903,13 +11843,13 @@
         <v>1.94617748393706</v>
       </c>
       <c r="D75">
-        <v>2.8481546871048198</v>
+        <v>28.908387069180701</v>
       </c>
       <c r="E75">
         <v>13.310067390991801</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>1995</v>
       </c>
@@ -11920,13 +11860,19 @@
         <v>2.9046401169163101</v>
       </c>
       <c r="D76">
-        <v>-7.3329491439114802</v>
+        <v>-15.0920254264989</v>
       </c>
       <c r="E76">
         <v>6.1528458598751703</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <v>1.63399671044108</v>
+      </c>
+      <c r="G76" s="2">
+        <v>9.2615348306329004</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>1996</v>
       </c>
@@ -11937,13 +11883,19 @@
         <v>5.6364281910172496</v>
       </c>
       <c r="D77">
-        <v>40.316935537926703</v>
+        <v>-2.2165468599247</v>
       </c>
       <c r="E77">
         <v>6.4899496914886603</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <v>5.4446740744838804</v>
+      </c>
+      <c r="G77" s="2">
+        <v>2.0111715205006999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>1997</v>
       </c>
@@ -11954,13 +11906,19 @@
         <v>8.0497437190152095</v>
       </c>
       <c r="D78">
-        <v>4.9142683801870204</v>
+        <v>-0.48686488697555302</v>
       </c>
       <c r="E78">
         <v>4.3619110939309804</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <v>5.6437393264022502</v>
+      </c>
+      <c r="G78" s="2">
+        <v>6.73329215199084</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>1998</v>
       </c>
@@ -11971,13 +11929,19 @@
         <v>3.5967026984990702</v>
       </c>
       <c r="D79">
-        <v>3.7304985017433401</v>
+        <v>-9.3948408194301596</v>
       </c>
       <c r="E79">
         <v>0.12894681960950999</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <v>0.94220289258539902</v>
+      </c>
+      <c r="G79" s="2">
+        <v>-0.79814068752556</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>1999</v>
       </c>
@@ -11988,13 +11952,19 @@
         <v>9.5372142776714703</v>
       </c>
       <c r="D80">
-        <v>9.26964224962936</v>
+        <v>32.594630974299697</v>
       </c>
       <c r="E80">
         <v>11.146444683562899</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <v>11.4809769039781</v>
+      </c>
+      <c r="G80" s="2">
+        <v>-1.6016190695225001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2000</v>
       </c>
@@ -12005,13 +11975,19 @@
         <v>0.87719298245613697</v>
       </c>
       <c r="D81">
-        <v>4.0797287786924397</v>
+        <v>19.618331519747599</v>
       </c>
       <c r="E81">
         <v>5.8020865906781998</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <v>3.5127612560741901</v>
+      </c>
+      <c r="G81" s="2">
+        <v>2.4068587942117898</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2001</v>
       </c>
@@ -12022,13 +11998,19 @@
         <v>9.9184782608695592</v>
       </c>
       <c r="D82">
-        <v>-3.9020527349899798</v>
+        <v>-13.0499616031404</v>
       </c>
       <c r="E82">
         <v>-0.78730536884394597</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <v>4.1551891793372997</v>
+      </c>
+      <c r="G82" s="2">
+        <v>-0.63824050818333</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2002</v>
       </c>
@@ -12039,13 +12021,19 @@
         <v>9.9567367119901302</v>
       </c>
       <c r="D83">
-        <v>-23.991917964461301</v>
+        <v>2.8481546871048198</v>
       </c>
       <c r="E83">
         <v>5.0633820938678697</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <v>8.4315710785658702</v>
+      </c>
+      <c r="G83" s="2">
+        <v>4.3452877287546796</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>2003</v>
       </c>
@@ -12056,13 +12044,19 @@
         <v>3.9654881681749301</v>
       </c>
       <c r="D84">
-        <v>58.526590641425301</v>
+        <v>-7.3329491439114802</v>
       </c>
       <c r="E84">
         <v>1.9810885734898001</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <v>3.62667652589808</v>
+      </c>
+      <c r="G84" s="2">
+        <v>4.3730583076632099</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2004</v>
       </c>
@@ -12073,13 +12067,19 @@
         <v>5.98221285107992</v>
       </c>
       <c r="D85">
-        <v>-30.177305758159299</v>
+        <v>40.316935537926703</v>
       </c>
       <c r="E85">
         <v>-0.489554497048374</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <v>4.5290965187586396</v>
+      </c>
+      <c r="G85" s="2">
+        <v>5.1231007558047299</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2005</v>
       </c>
@@ -12090,13 +12090,19 @@
         <v>10.2790389226139</v>
       </c>
       <c r="D86">
-        <v>24.0967587933497</v>
+        <v>4.9142683801870204</v>
       </c>
       <c r="E86">
         <v>3.3959424977663399</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <v>7.3522616789174302</v>
+      </c>
+      <c r="G86" s="2">
+        <v>5.8777437978957998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>2006</v>
       </c>
@@ -12107,13 +12113,19 @@
         <v>1.9011934499029199</v>
       </c>
       <c r="D87">
-        <v>-27.935482382675801</v>
+        <v>3.7304985017433401</v>
       </c>
       <c r="E87">
         <v>8.9295389019842393</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <v>3.1806295432933598</v>
+      </c>
+      <c r="G87" s="2">
+        <v>9.2122811137238294</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>2007</v>
       </c>
@@ -12124,13 +12136,19 @@
         <v>4.1626946298061398</v>
       </c>
       <c r="D88">
-        <v>15.866816069988699</v>
+        <v>9.26964224962936</v>
       </c>
       <c r="E88">
         <v>3.3165187780669099</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <v>2.89263898066827</v>
+      </c>
+      <c r="G88" s="2">
+        <v>10.576338394414</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>2008</v>
       </c>
@@ -12141,13 +12159,19 @@
         <v>7.0959183101766898</v>
       </c>
       <c r="D89">
-        <v>-10.088288043286701</v>
+        <v>4.0797287786924397</v>
       </c>
       <c r="E89">
         <v>8.3623422875560998</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <v>7.5840571152043603</v>
+      </c>
+      <c r="G89" s="2">
+        <v>9.65160189410099</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2009</v>
       </c>
@@ -12158,13 +12182,19 @@
         <v>0.80793194040455796</v>
       </c>
       <c r="D90">
-        <v>4.66525619320596</v>
+        <v>-3.9020527349899798</v>
       </c>
       <c r="E90">
         <v>2.0458562525016402</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <v>-0.61353544092411005</v>
+      </c>
+      <c r="G90" s="2">
+        <v>1.6666775963530001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>2010</v>
       </c>
@@ -12175,13 +12205,19 @@
         <v>0.53716859055326405</v>
       </c>
       <c r="D91">
-        <v>47.684754651389703</v>
+        <v>-23.991917964461301</v>
       </c>
       <c r="E91">
         <v>3.2234142006519702</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <v>-0.32264615369515998</v>
+      </c>
+      <c r="G91" s="2">
+        <v>11.1580719271177</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>2011</v>
       </c>
@@ -12192,13 +12228,19 @@
         <v>-0.53361238725304405</v>
       </c>
       <c r="D92">
-        <v>-17.152157042171201</v>
+        <v>58.526590641425301</v>
       </c>
       <c r="E92">
         <v>4.6452566576933201</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <v>4.5040233076495904</v>
+      </c>
+      <c r="G92" s="2">
+        <v>6.8609237965196099</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>2012</v>
       </c>
@@ -12209,13 +12251,19 @@
         <v>2.1959987528443299</v>
       </c>
       <c r="D93">
-        <v>4.2176542630345502</v>
+        <v>-30.177305758159299</v>
       </c>
       <c r="E93">
         <v>7.5183379648894304</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <v>4.2476698672302602</v>
+      </c>
+      <c r="G93" s="2">
+        <v>6.6814057136362903</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>2013</v>
       </c>
@@ -12226,13 +12274,19 @@
         <v>4.87914802132362</v>
       </c>
       <c r="D94">
-        <v>9.9146663228252994</v>
+        <v>24.0967587933497</v>
       </c>
       <c r="E94">
         <v>2.6986399909532102</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <v>5.42174683261561</v>
+      </c>
+      <c r="G94" s="2">
+        <v>5.9730313339573202</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>2014</v>
       </c>
@@ -12243,13 +12297,19 @@
         <v>-0.87232682363790603</v>
       </c>
       <c r="D95">
-        <v>-11.3931389022364</v>
+        <v>-27.935482382675801</v>
       </c>
       <c r="E95">
         <v>1.5742084221059101</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <v>-2.5229046017499099</v>
+      </c>
+      <c r="G95" s="2">
+        <v>3.7472649061890499</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>2015</v>
       </c>
@@ -12260,13 +12320,19 @@
         <v>9.4578647137798306</v>
       </c>
       <c r="D96">
-        <v>-21.2270629034577</v>
+        <v>15.866816069988699</v>
       </c>
       <c r="E96">
         <v>3.4653377797251999</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <v>6.6155158807324597</v>
+      </c>
+      <c r="G96" s="2">
+        <v>2.3727967631526901</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>2016</v>
       </c>
@@ -12277,13 +12343,19 @@
         <v>16.2960119521526</v>
       </c>
       <c r="D97">
-        <v>27.211581049774399</v>
+        <v>-10.088288043286701</v>
       </c>
       <c r="E97">
         <v>2.6978804332850101</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <v>9.4597028975817796</v>
+      </c>
+      <c r="G97" s="2">
+        <v>2.45380432681814</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>2017</v>
       </c>
@@ -12294,13 +12366,19 @@
         <v>3.4245542259084201</v>
       </c>
       <c r="D98">
-        <v>2.8793329551197502</v>
+        <v>4.66525619320596</v>
       </c>
       <c r="E98">
         <v>2.94696058572424</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <v>3.0592485165454</v>
+      </c>
+      <c r="G98" s="2">
+        <v>2.3616051901795498</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>2018</v>
       </c>
@@ -12310,11 +12388,20 @@
       <c r="C99">
         <v>-1.4940228009790999</v>
       </c>
+      <c r="D99">
+        <v>47.684754651389703</v>
+      </c>
       <c r="E99">
         <v>7.68612615157262</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <v>3.6617771156346501</v>
+      </c>
+      <c r="G99" s="2">
+        <v>4.0594482916463903</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>2019</v>
       </c>
@@ -12324,11 +12411,20 @@
       <c r="C100">
         <v>-4.9193128253492098E-2</v>
       </c>
+      <c r="D100">
+        <v>-17.152157042171201</v>
+      </c>
       <c r="E100">
         <v>3.5400174701519398</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <v>-0.92263513740425696</v>
+      </c>
+      <c r="G100" s="2">
+        <v>3.16369862469034</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>2020</v>
       </c>
@@ -12338,11 +12434,20 @@
       <c r="C101">
         <v>-13.416251611903</v>
       </c>
+      <c r="D101">
+        <v>4.2176542630345502</v>
+      </c>
       <c r="E101">
         <v>1.03248033284262</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <v>-7.5915623037303801</v>
+      </c>
+      <c r="G101" s="2">
+        <v>-11.869828663848701</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>2021</v>
       </c>
@@ -12352,11 +12457,20 @@
       <c r="C102">
         <v>8.1226852807999599</v>
       </c>
+      <c r="D102">
+        <v>9.9146663228252994</v>
+      </c>
       <c r="E102">
         <v>4.6433793368510798</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <v>6.3893139547329696</v>
+      </c>
+      <c r="G102" s="2">
+        <v>15.4816563888501</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2022</v>
       </c>
@@ -12366,11 +12480,20 @@
       <c r="C103">
         <v>0.515899525952634</v>
       </c>
+      <c r="D103">
+        <v>-11.3931389022364</v>
+      </c>
       <c r="E103">
         <v>4.5523514414863397</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <v>0.90881374412055005</v>
+      </c>
+      <c r="G103" s="2">
+        <v>3.3351046339961399</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2023</v>
       </c>
@@ -12380,11 +12503,20 @@
       <c r="C104">
         <v>9.4342737305761109</v>
       </c>
+      <c r="D104">
+        <v>-21.2270629034577</v>
+      </c>
       <c r="E104">
         <v>-2.0433637295013498</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104">
+        <v>3.7374032599298301</v>
+      </c>
+      <c r="G104" s="2">
+        <v>-1.4314365974834</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>2024</v>
       </c>
@@ -12394,11 +12526,20 @@
       <c r="C105">
         <v>3.03167249320065</v>
       </c>
+      <c r="D105">
+        <v>27.211581049774399</v>
+      </c>
       <c r="E105">
         <v>5.5725445150255801</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105">
+        <v>4.8360981798516596</v>
+      </c>
+      <c r="G105" s="2">
+        <v>3.14778980342005</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>2025</v>
       </c>
@@ -12408,8 +12549,17 @@
       <c r="C106">
         <v>1.49680641814447</v>
       </c>
+      <c r="D106">
+        <v>2.8793329551197502</v>
+      </c>
       <c r="E106">
         <v>5.5786226638611298</v>
+      </c>
+      <c r="F106">
+        <v>3.15216443165242</v>
+      </c>
+      <c r="G106" s="2">
+        <v>3.52700228627072</v>
       </c>
     </row>
   </sheetData>
@@ -12420,18 +12570,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>401</v>
       </c>
@@ -12454,7 +12604,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>406</v>
       </c>
@@ -12477,7 +12627,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>407</v>
       </c>
@@ -12500,7 +12650,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>408</v>
       </c>
@@ -12523,7 +12673,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>409</v>
       </c>
@@ -12546,7 +12696,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>410</v>
       </c>
@@ -12569,7 +12719,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>411</v>
       </c>
@@ -12592,7 +12742,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>412</v>
       </c>
@@ -12615,7 +12765,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>422</v>
       </c>
@@ -12638,7 +12788,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>413</v>
       </c>
@@ -12661,7 +12811,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>414</v>
       </c>
@@ -12684,7 +12834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>415</v>
       </c>
@@ -12707,7 +12857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>416</v>
       </c>
@@ -12730,7 +12880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>417</v>
       </c>
@@ -12761,18 +12911,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>401</v>
       </c>
@@ -12795,7 +12945,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>407</v>
       </c>
@@ -12818,7 +12968,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>418</v>
       </c>
@@ -12841,7 +12991,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>419</v>
       </c>
@@ -12864,7 +13014,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>408</v>
       </c>
@@ -12887,7 +13037,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>420</v>
       </c>
@@ -12910,7 +13060,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>409</v>
       </c>
@@ -12933,7 +13083,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>410</v>
       </c>
@@ -12956,7 +13106,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>421</v>
       </c>
@@ -12979,7 +13129,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>411</v>
       </c>
@@ -13002,7 +13152,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>422</v>
       </c>
@@ -13025,7 +13175,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>413</v>
       </c>
@@ -13048,7 +13198,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>414</v>
       </c>
@@ -13071,7 +13221,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>415</v>
       </c>
@@ -13094,7 +13244,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>416</v>
       </c>
@@ -13117,7 +13267,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>417</v>
       </c>
@@ -13140,7 +13290,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>406</v>
       </c>
@@ -13163,7 +13313,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>412</v>
       </c>
@@ -13186,7 +13336,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
     </row>
   </sheetData>
@@ -13197,18 +13347,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A68304E-ADCB-4635-8C75-D88C3A2635CC}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>401</v>
       </c>
@@ -13231,7 +13381,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>406</v>
       </c>
@@ -13254,7 +13404,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>407</v>
       </c>
@@ -13277,7 +13427,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>408</v>
       </c>
@@ -13300,7 +13450,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>409</v>
       </c>
@@ -13323,7 +13473,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>410</v>
       </c>
@@ -13346,7 +13496,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>411</v>
       </c>
@@ -13369,7 +13519,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>412</v>
       </c>
@@ -13392,7 +13542,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>422</v>
       </c>
@@ -13415,7 +13565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>413</v>
       </c>
@@ -13438,7 +13588,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>414</v>
       </c>
@@ -13461,7 +13611,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>415</v>
       </c>
@@ -13484,7 +13634,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>416</v>
       </c>
@@ -13507,7 +13657,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>417</v>
       </c>
@@ -13533,4 +13683,349 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F7F377-515B-4243-A110-355A024FF604}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D2" s="3">
+        <v>-0.5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7">
+        <v>-1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C8" t="s">
+        <v>436</v>
+      </c>
+      <c r="D8">
+        <v>-1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C9" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9">
+        <v>-1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D11">
+        <v>-2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C12" t="s">
+        <v>436</v>
+      </c>
+      <c r="D12">
+        <v>-2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C13" t="s">
+        <v>437</v>
+      </c>
+      <c r="D13">
+        <v>-2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2027</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C14" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2027</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C15" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2027</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2027</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C17" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2027</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C18" t="s">
+        <v>434</v>
+      </c>
+      <c r="D18">
+        <v>-0.9</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2027</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C19" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2027</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C20" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2027</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2027</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2027</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C23" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2027</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C24" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C25" t="s">
+        <v>437</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/BCRP data.xlsx
+++ b/BCRP data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Mesa de Inversiones\Bottom-Up\Franco\Semestral - Trabajos\Renzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9C4A9F-E3E1-4BEF-A712-1AE0F61B1446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF77B3FA-05C7-48E4-B492-6273E974992B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="450">
   <si>
     <t>PN01730AM</t>
   </si>
@@ -1417,6 +1417,9 @@
   </si>
   <si>
     <t>Meeting</t>
+  </si>
+  <si>
+    <t>Adrian Armas BCRP</t>
   </si>
 </sst>
 </file>
@@ -1566,6 +1569,50 @@
         <a:xfrm>
           <a:off x="6286500" y="1356919"/>
           <a:ext cx="4070842" cy="1256099"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>48956</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>56333</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>101812</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8594158D-FA0C-C7B1-18B4-98322F2ADC9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7033956" y="2818583"/>
+          <a:ext cx="3443544" cy="2255279"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13772,6 +13819,12 @@
       <c r="C6" t="s">
         <v>434</v>
       </c>
+      <c r="D6">
+        <v>-0.7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">

--- a/BCRP data.xlsx
+++ b/BCRP data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Mesa de Inversiones\Bottom-Up\Franco\Semestral - Trabajos\Renzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF77B3FA-05C7-48E4-B492-6273E974992B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C609BCD0-A949-4C3C-8C0D-9560249DB160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13820,7 +13820,7 @@
         <v>434</v>
       </c>
       <c r="D6">
-        <v>-0.7</v>
+        <v>0.7</v>
       </c>
       <c r="E6" t="s">
         <v>449</v>
@@ -13837,7 +13837,7 @@
         <v>435</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>448</v>
@@ -13854,7 +13854,7 @@
         <v>436</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
         <v>448</v>
@@ -13871,7 +13871,7 @@
         <v>437</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
         <v>448</v>
@@ -13899,7 +13899,7 @@
         <v>435</v>
       </c>
       <c r="D11">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>448</v>
@@ -13916,7 +13916,7 @@
         <v>436</v>
       </c>
       <c r="D12">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
         <v>448</v>
@@ -13933,7 +13933,7 @@
         <v>437</v>
       </c>
       <c r="D13">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E13" t="s">
         <v>448</v>
